--- a/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
+++ b/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
@@ -515,7 +515,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,7 +666,6 @@
     <row r="4">
       <c r="A4" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -699,7 +698,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -732,7 +730,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -765,7 +762,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -798,7 +794,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -824,14 +819,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -857,14 +851,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -887,7 +880,6 @@
     <row r="11">
       <c r="A11" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -910,7 +902,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -938,7 +929,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -966,7 +956,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -994,7 +983,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -1022,7 +1010,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -1046,7 +1033,6 @@
     <row r="17">
       <c r="A17" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -1074,7 +1060,6 @@
     <row r="18">
       <c r="A18" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -1102,7 +1087,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -1130,7 +1114,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -1154,7 +1137,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -1182,7 +1164,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -1210,7 +1191,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -1238,7 +1218,6 @@
     <row r="24">
       <c r="A24" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -1266,7 +1245,6 @@
     <row r="25">
       <c r="A25" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -1289,7 +1267,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -1312,7 +1289,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -1335,7 +1311,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -1358,7 +1333,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -1381,7 +1355,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -1404,7 +1377,6 @@
     <row r="31">
       <c r="A31" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -1427,7 +1399,6 @@
     <row r="32">
       <c r="A32" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -1450,7 +1421,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -1511,7 +1481,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1662,7 +1632,6 @@
     <row r="4">
       <c r="A4" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -1695,7 +1664,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -1728,7 +1696,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -1761,7 +1728,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -1794,7 +1760,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -1820,14 +1785,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -1853,14 +1817,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -1883,7 +1846,6 @@
     <row r="11">
       <c r="A11" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -1906,7 +1868,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -1934,7 +1895,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -1962,7 +1922,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -1990,7 +1949,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -2018,7 +1976,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -2042,7 +1999,6 @@
     <row r="17">
       <c r="A17" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -2070,7 +2026,6 @@
     <row r="18">
       <c r="A18" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -2098,7 +2053,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -2126,7 +2080,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -2150,7 +2103,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -2178,7 +2130,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -2206,7 +2157,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -2234,7 +2184,6 @@
     <row r="24">
       <c r="A24" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -2262,7 +2211,6 @@
     <row r="25">
       <c r="A25" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -2285,7 +2233,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -2308,7 +2255,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -2331,7 +2277,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -2354,7 +2299,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -2377,7 +2321,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -2400,7 +2343,6 @@
     <row r="31">
       <c r="A31" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -2423,7 +2365,6 @@
     <row r="32">
       <c r="A32" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -2446,7 +2387,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -2469,7 +2409,6 @@
     <row r="34">
       <c r="A34" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -2530,7 +2469,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2681,7 +2620,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -2714,7 +2652,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -2747,7 +2684,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -2780,7 +2716,6 @@
     <row r="7">
       <c r="A7" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -2813,7 +2748,6 @@
     <row r="8">
       <c r="A8" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -2839,14 +2773,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -2872,14 +2805,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -2902,7 +2834,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -2925,7 +2856,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -2953,7 +2883,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -2981,7 +2910,6 @@
     <row r="14">
       <c r="A14" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -3009,7 +2937,6 @@
     <row r="15">
       <c r="A15" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -3037,7 +2964,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -3061,7 +2987,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -3089,7 +3014,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -3117,7 +3041,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -3145,7 +3068,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -3169,7 +3091,6 @@
     <row r="21">
       <c r="A21" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -3197,7 +3118,6 @@
     <row r="22">
       <c r="A22" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -3225,7 +3145,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -3253,7 +3172,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -3281,7 +3199,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -3304,7 +3221,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -3327,7 +3243,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -3350,7 +3265,6 @@
     <row r="28">
       <c r="A28" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -3373,7 +3287,6 @@
     <row r="29">
       <c r="A29" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -3396,7 +3309,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -3419,7 +3331,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -3442,7 +3353,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -3465,7 +3375,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -3526,7 +3435,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3677,7 +3586,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -3710,7 +3618,6 @@
     <row r="5">
       <c r="A5" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -3743,7 +3650,6 @@
     <row r="6">
       <c r="A6" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -3776,7 +3682,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -3809,7 +3714,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -3835,14 +3739,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -3868,14 +3771,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -3898,7 +3800,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -3921,7 +3822,6 @@
     <row r="12">
       <c r="A12" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -3949,7 +3849,6 @@
     <row r="13">
       <c r="A13" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -3977,7 +3876,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -4005,7 +3903,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -4033,7 +3930,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -4057,7 +3953,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -4085,7 +3980,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -4113,7 +4007,6 @@
     <row r="19">
       <c r="A19" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -4141,7 +4034,6 @@
     <row r="20">
       <c r="A20" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -4165,7 +4057,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -4193,7 +4084,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -4221,7 +4111,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -4249,7 +4138,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -4277,7 +4165,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -4300,7 +4187,6 @@
     <row r="26">
       <c r="A26" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -4323,7 +4209,6 @@
     <row r="27">
       <c r="A27" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -4346,7 +4231,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -4369,7 +4253,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -4392,7 +4275,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -4415,7 +4297,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -4438,7 +4319,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -4461,7 +4341,6 @@
     <row r="33">
       <c r="A33" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -4484,7 +4363,6 @@
     <row r="34">
       <c r="A34" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>
@@ -4545,7 +4423,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4696,7 +4574,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -4729,7 +4606,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -4762,7 +4638,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -4795,7 +4670,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -4828,7 +4702,6 @@
     <row r="8">
       <c r="A8" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -4854,14 +4727,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -4887,14 +4759,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -4917,7 +4788,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -4940,7 +4810,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -4968,7 +4837,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -4996,7 +4864,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -5024,7 +4891,6 @@
     <row r="15">
       <c r="A15" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -5052,7 +4918,6 @@
     <row r="16">
       <c r="A16" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -5076,7 +4941,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -5104,7 +4968,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -5132,7 +4995,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -5160,7 +5022,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -5184,7 +5045,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -5212,7 +5072,6 @@
     <row r="22">
       <c r="A22" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -5240,7 +5099,6 @@
     <row r="23">
       <c r="A23" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -5268,7 +5126,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -5296,7 +5153,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -5319,7 +5175,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -5342,7 +5197,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -5365,7 +5219,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -5388,7 +5241,6 @@
     <row r="29">
       <c r="A29" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -5411,7 +5263,6 @@
     <row r="30">
       <c r="A30" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -5434,7 +5285,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -5457,7 +5307,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -5480,7 +5329,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -5503,7 +5351,6 @@
     <row r="34">
       <c r="A34" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -5564,7 +5411,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5715,7 +5562,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -5748,7 +5594,6 @@
     <row r="5">
       <c r="A5" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -5781,7 +5626,6 @@
     <row r="6">
       <c r="A6" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -5814,7 +5658,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -5847,7 +5690,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -5873,14 +5715,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -5906,14 +5747,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -5936,7 +5776,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -5959,7 +5798,6 @@
     <row r="12">
       <c r="A12" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -5987,7 +5825,6 @@
     <row r="13">
       <c r="A13" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -6015,7 +5852,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -6043,7 +5879,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -6071,7 +5906,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -6095,7 +5929,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -6123,7 +5956,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -6151,7 +5983,6 @@
     <row r="19">
       <c r="A19" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -6179,7 +6010,6 @@
     <row r="20">
       <c r="A20" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -6203,7 +6033,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -6231,7 +6060,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -6259,7 +6087,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -6287,7 +6114,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -6315,7 +6141,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -6338,7 +6163,6 @@
     <row r="26">
       <c r="A26" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -6361,7 +6185,6 @@
     <row r="27">
       <c r="A27" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -6384,7 +6207,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -6407,7 +6229,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -6430,7 +6251,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -6453,7 +6273,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -6476,7 +6295,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -6499,7 +6317,6 @@
     <row r="33">
       <c r="A33" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -6522,7 +6339,6 @@
     <row r="34">
       <c r="A34" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>
@@ -6583,7 +6399,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6734,7 +6550,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -6767,7 +6582,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -6800,7 +6614,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -6833,7 +6646,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -6866,7 +6678,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -6892,14 +6703,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -6925,14 +6735,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -6955,7 +6764,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -6978,7 +6786,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -7006,7 +6813,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -7034,7 +6840,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -7062,7 +6867,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -7090,7 +6894,6 @@
     <row r="16">
       <c r="A16" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -7114,7 +6917,6 @@
     <row r="17">
       <c r="A17" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -7142,7 +6944,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -7170,7 +6971,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -7198,7 +6998,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -7222,7 +7021,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -7250,7 +7048,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -7278,7 +7075,6 @@
     <row r="23">
       <c r="A23" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -7306,7 +7102,6 @@
     <row r="24">
       <c r="A24" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -7334,7 +7129,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -7357,7 +7151,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -7380,7 +7173,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -7403,7 +7195,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -7426,7 +7217,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -7449,7 +7239,6 @@
     <row r="30">
       <c r="A30" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -7472,7 +7261,6 @@
     <row r="31">
       <c r="A31" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -7533,7 +7321,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7684,7 +7472,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -7717,7 +7504,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -7750,7 +7536,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -7783,7 +7568,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -7816,7 +7600,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -7842,14 +7625,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -7875,14 +7657,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -7905,7 +7686,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -7928,7 +7708,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -7956,7 +7735,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -7984,7 +7762,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -8012,7 +7789,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -8040,7 +7816,6 @@
     <row r="16">
       <c r="A16" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -8064,7 +7839,6 @@
     <row r="17">
       <c r="A17" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -8092,7 +7866,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -8120,7 +7893,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -8148,7 +7920,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -8172,7 +7943,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -8200,7 +7970,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -8228,7 +7997,6 @@
     <row r="23">
       <c r="A23" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -8256,7 +8024,6 @@
     <row r="24">
       <c r="A24" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -8284,7 +8051,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -8307,7 +8073,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -8330,7 +8095,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -8353,7 +8117,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -8376,7 +8139,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -8399,7 +8161,6 @@
     <row r="30">
       <c r="A30" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -8422,7 +8183,6 @@
     <row r="31">
       <c r="A31" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -8445,7 +8205,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -8468,7 +8227,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -8491,7 +8249,6 @@
     <row r="34">
       <c r="A34" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -8552,7 +8309,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8703,7 +8460,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -8736,7 +8492,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -8769,7 +8524,6 @@
     <row r="6">
       <c r="A6" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -8802,7 +8556,6 @@
     <row r="7">
       <c r="A7" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -8835,7 +8588,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -8861,14 +8613,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -8894,14 +8645,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -8924,7 +8674,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -8947,7 +8696,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -8975,7 +8723,6 @@
     <row r="13">
       <c r="A13" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -9003,7 +8750,6 @@
     <row r="14">
       <c r="A14" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -9031,7 +8777,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -9059,7 +8804,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -9083,7 +8827,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -9111,7 +8854,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -9139,7 +8881,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -9167,7 +8908,6 @@
     <row r="20">
       <c r="A20" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -9191,7 +8931,6 @@
     <row r="21">
       <c r="A21" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -9219,7 +8958,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -9247,7 +8985,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -9275,7 +9012,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -9303,7 +9039,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -9326,7 +9061,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -9349,7 +9083,6 @@
     <row r="27">
       <c r="A27" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -9372,7 +9105,6 @@
     <row r="28">
       <c r="A28" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -9395,7 +9127,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -9418,7 +9149,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -9441,7 +9171,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -9464,7 +9193,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -9487,7 +9215,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -9548,7 +9275,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9699,7 +9426,6 @@
     <row r="4">
       <c r="A4" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -9732,7 +9458,6 @@
     <row r="5">
       <c r="A5" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -9765,7 +9490,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -9798,7 +9522,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -9831,7 +9554,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -9857,14 +9579,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -9890,14 +9611,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -9920,7 +9640,6 @@
     <row r="11">
       <c r="A11" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -9943,7 +9662,6 @@
     <row r="12">
       <c r="A12" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -9971,7 +9689,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -9999,7 +9716,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -10027,7 +9743,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -10055,7 +9770,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -10079,7 +9793,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -10107,7 +9820,6 @@
     <row r="18">
       <c r="A18" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -10135,7 +9847,6 @@
     <row r="19">
       <c r="A19" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -10163,7 +9874,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -10187,7 +9897,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -10215,7 +9924,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -10243,7 +9951,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -10271,7 +9978,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -10299,7 +10005,6 @@
     <row r="25">
       <c r="A25" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -10322,7 +10027,6 @@
     <row r="26">
       <c r="A26" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -10345,7 +10049,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -10368,7 +10071,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -10391,7 +10093,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -10414,7 +10115,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -10437,7 +10137,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -10460,7 +10159,6 @@
     <row r="32">
       <c r="A32" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -10483,7 +10181,6 @@
     <row r="33">
       <c r="A33" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -10506,7 +10203,6 @@
     <row r="34">
       <c r="A34" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -10567,7 +10263,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10718,7 +10414,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -10751,7 +10446,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -10784,7 +10478,6 @@
     <row r="6">
       <c r="A6" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -10817,7 +10510,6 @@
     <row r="7">
       <c r="A7" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -10850,7 +10542,6 @@
     <row r="8">
       <c r="A8" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -10876,14 +10567,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -10909,14 +10599,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -10939,7 +10628,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -10962,7 +10650,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -10990,7 +10677,6 @@
     <row r="13">
       <c r="A13" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -11018,7 +10704,6 @@
     <row r="14">
       <c r="A14" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -11046,7 +10731,6 @@
     <row r="15">
       <c r="A15" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -11074,7 +10758,6 @@
     <row r="16">
       <c r="A16" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -11098,7 +10781,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -11126,7 +10808,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -11154,7 +10835,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -11182,7 +10862,6 @@
     <row r="20">
       <c r="A20" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -11206,7 +10885,6 @@
     <row r="21">
       <c r="A21" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -11234,7 +10912,6 @@
     <row r="22">
       <c r="A22" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -11262,7 +10939,6 @@
     <row r="23">
       <c r="A23" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -11290,7 +10966,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -11318,7 +10993,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -11341,7 +11015,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -11364,7 +11037,6 @@
     <row r="27">
       <c r="A27" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -11387,7 +11059,6 @@
     <row r="28">
       <c r="A28" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -11410,7 +11081,6 @@
     <row r="29">
       <c r="A29" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -11433,7 +11103,6 @@
     <row r="30">
       <c r="A30" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -11456,7 +11125,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -11479,7 +11147,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -11502,7 +11169,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -11563,7 +11229,7 @@
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="89" customWidth="1" min="19" max="19"/>
+    <col width="131" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11714,7 +11380,6 @@
     <row r="4">
       <c r="A4" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -11747,7 +11412,6 @@
     <row r="5">
       <c r="A5" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -11780,7 +11444,6 @@
     <row r="6">
       <c r="A6" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -11813,7 +11476,6 @@
     <row r="7">
       <c r="A7" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -11846,7 +11508,6 @@
     <row r="8">
       <c r="A8" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -11872,14 +11533,13 @@
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE: blocca tutto il giorno stesso e tutto il giorno successivo</t>
+          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -11905,14 +11565,13 @@
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso: blocca tutto il giorno</t>
+          <t>congresso, blocca tutto il giorno</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -11935,7 +11594,6 @@
     <row r="11">
       <c r="A11" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -11958,7 +11616,6 @@
     <row r="12">
       <c r="A12" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -11986,7 +11643,6 @@
     <row r="13">
       <c r="A13" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -12014,7 +11670,6 @@
     <row r="14">
       <c r="A14" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -12042,7 +11697,6 @@
     <row r="15">
       <c r="A15" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -12070,7 +11724,6 @@
     <row r="16">
       <c r="A16" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -12094,7 +11747,6 @@
     <row r="17">
       <c r="A17" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -12122,7 +11774,6 @@
     <row r="18">
       <c r="A18" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -12150,7 +11801,6 @@
     <row r="19">
       <c r="A19" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -12178,7 +11828,6 @@
     <row r="20">
       <c r="A20" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -12202,7 +11851,6 @@
     <row r="21">
       <c r="A21" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -12230,7 +11878,6 @@
     <row r="22">
       <c r="A22" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -12258,7 +11905,6 @@
     <row r="23">
       <c r="A23" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -12286,7 +11932,6 @@
     <row r="24">
       <c r="A24" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -12314,7 +11959,6 @@
     <row r="25">
       <c r="A25" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -12337,7 +11981,6 @@
     <row r="26">
       <c r="A26" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -12360,7 +12003,6 @@
     <row r="27">
       <c r="A27" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -12383,7 +12025,6 @@
     <row r="28">
       <c r="A28" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -12406,7 +12047,6 @@
     <row r="29">
       <c r="A29" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -12429,7 +12069,6 @@
     <row r="30">
       <c r="A30" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -12452,7 +12091,6 @@
     <row r="31">
       <c r="A31" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -12475,7 +12113,6 @@
     <row r="32">
       <c r="A32" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -12498,7 +12135,6 @@
     <row r="33">
       <c r="A33" s="9">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -12521,7 +12157,6 @@
     <row r="34">
       <c r="A34" s="5">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
-        <v/>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>

--- a/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
+++ b/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
@@ -664,8 +664,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -696,8 +697,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -728,8 +730,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -760,8 +763,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -792,8 +796,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -824,8 +829,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -856,8 +862,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -878,8 +885,9 @@
       <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -900,8 +908,9 @@
       <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -927,8 +936,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -954,8 +964,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -981,8 +992,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -1008,8 +1020,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -1031,8 +1044,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -1058,8 +1072,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -1085,8 +1100,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -1112,8 +1128,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -1135,8 +1152,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -1162,8 +1180,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -1189,8 +1208,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -1216,8 +1236,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -1243,8 +1264,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -1265,8 +1287,9 @@
       <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -1287,8 +1310,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -1309,8 +1333,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -1331,8 +1356,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -1353,8 +1379,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -1375,8 +1402,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -1397,8 +1425,9 @@
       <c r="P31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5">
+      <c r="A32" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -1419,8 +1448,9 @@
       <c r="P32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -1630,8 +1660,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -1662,8 +1693,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -1694,8 +1726,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -1726,8 +1759,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -1758,8 +1792,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -1790,8 +1825,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -1822,8 +1858,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -1844,8 +1881,9 @@
       <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -1866,8 +1904,9 @@
       <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -1893,8 +1932,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -1920,8 +1960,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -1947,8 +1988,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -1974,8 +2016,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -1997,8 +2040,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -2024,8 +2068,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -2051,8 +2096,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -2078,8 +2124,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -2101,8 +2148,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -2128,8 +2176,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -2155,8 +2204,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -2182,8 +2232,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -2209,8 +2260,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -2231,8 +2283,9 @@
       <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -2253,8 +2306,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -2275,8 +2329,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -2297,8 +2352,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -2319,8 +2375,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -2341,8 +2398,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -2363,8 +2421,9 @@
       <c r="P31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5">
+      <c r="A32" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -2385,8 +2444,9 @@
       <c r="P32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -2407,8 +2467,9 @@
       <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -2618,8 +2679,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -2650,8 +2712,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -2682,8 +2745,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -2714,8 +2778,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -2746,8 +2811,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -2778,8 +2844,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -2810,8 +2877,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -2832,8 +2900,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -2854,8 +2923,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -2881,8 +2951,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -2908,8 +2979,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -2935,8 +3007,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -2962,8 +3035,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -2985,8 +3059,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -3012,8 +3087,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -3039,8 +3115,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -3066,8 +3143,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -3089,8 +3167,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -3116,8 +3195,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -3143,8 +3223,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -3170,8 +3251,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -3197,8 +3279,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -3219,8 +3302,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -3241,8 +3325,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -3263,8 +3348,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5">
+      <c r="A28" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -3285,8 +3371,9 @@
       <c r="P28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5">
+      <c r="A29" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -3307,8 +3394,9 @@
       <c r="P29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -3329,8 +3417,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -3351,8 +3440,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -3373,8 +3463,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -3584,8 +3675,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -3616,8 +3708,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -3648,8 +3741,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -3680,8 +3774,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -3712,8 +3807,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -3744,8 +3840,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -3776,8 +3873,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -3798,8 +3896,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -3820,8 +3919,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -3847,8 +3947,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -3874,8 +3975,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -3901,8 +4003,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -3928,8 +4031,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -3951,8 +4055,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -3978,8 +4083,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -4005,8 +4111,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -4032,8 +4139,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -4055,8 +4163,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -4082,8 +4191,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -4109,8 +4219,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -4136,8 +4247,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -4163,8 +4275,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -4185,8 +4298,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -4207,8 +4321,9 @@
       <c r="P26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -4229,8 +4344,9 @@
       <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -4251,8 +4367,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -4273,8 +4390,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -4295,8 +4413,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -4317,8 +4436,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -4339,8 +4459,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5">
+      <c r="A33" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -4361,8 +4482,9 @@
       <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5">
+      <c r="A34" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>
@@ -4572,8 +4694,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -4604,8 +4727,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -4636,8 +4760,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -4668,8 +4793,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -4700,8 +4826,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -4732,8 +4859,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -4764,8 +4892,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -4786,8 +4915,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -4808,8 +4938,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -4835,8 +4966,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -4862,8 +4994,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -4889,8 +5022,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -4916,8 +5050,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -4939,8 +5074,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -4966,8 +5102,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -4993,8 +5130,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -5020,8 +5158,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -5043,8 +5182,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -5070,8 +5210,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -5097,8 +5238,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -5124,8 +5266,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -5151,8 +5294,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -5173,8 +5317,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -5195,8 +5340,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -5217,8 +5363,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -5239,8 +5386,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5">
+      <c r="A29" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -5261,8 +5409,9 @@
       <c r="P29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -5283,8 +5432,9 @@
       <c r="P30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -5305,8 +5455,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -5327,8 +5478,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -5349,8 +5501,9 @@
       <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -5560,8 +5713,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -5592,8 +5746,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -5624,8 +5779,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -5656,8 +5812,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -5688,8 +5845,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -5720,8 +5878,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -5752,8 +5911,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -5774,8 +5934,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -5796,8 +5957,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -5823,8 +5985,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -5850,8 +6013,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -5877,8 +6041,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -5904,8 +6069,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -5927,8 +6093,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -5954,8 +6121,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -5981,8 +6149,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -6008,8 +6177,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -6031,8 +6201,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -6058,8 +6229,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -6085,8 +6257,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -6112,8 +6285,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -6139,8 +6313,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -6161,8 +6336,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -6183,8 +6359,9 @@
       <c r="P26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -6205,8 +6382,9 @@
       <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -6227,8 +6405,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -6249,8 +6428,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -6271,8 +6451,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -6293,8 +6474,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -6315,8 +6497,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5">
+      <c r="A33" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -6337,8 +6520,9 @@
       <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5">
+      <c r="A34" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>
@@ -6548,8 +6732,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -6580,8 +6765,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -6612,8 +6798,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -6644,8 +6831,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -6676,8 +6864,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -6708,8 +6897,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -6740,8 +6930,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -6762,8 +6953,9 @@
       <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -6784,8 +6976,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -6811,8 +7004,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -6838,8 +7032,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -6865,8 +7060,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -6892,8 +7088,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -6915,8 +7112,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -6942,8 +7140,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -6969,8 +7168,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -6996,8 +7196,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -7019,8 +7220,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -7046,8 +7248,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -7073,8 +7276,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -7100,8 +7304,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -7127,8 +7332,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -7149,8 +7355,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -7171,8 +7378,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -7193,8 +7401,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -7215,8 +7424,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -7237,8 +7447,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -7259,8 +7470,9 @@
       <c r="P30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -7470,8 +7682,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -7502,8 +7715,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -7534,8 +7748,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -7566,8 +7781,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -7598,8 +7814,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -7630,8 +7847,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -7662,8 +7880,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>7</v>
@@ -7684,8 +7903,9 @@
       <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -7706,8 +7926,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -7733,8 +7954,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -7760,8 +7982,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -7787,8 +8010,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -7814,8 +8038,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -7837,8 +8062,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>14</v>
@@ -7864,8 +8090,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -7891,8 +8118,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -7918,8 +8146,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -7941,8 +8170,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -7968,8 +8198,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -7995,8 +8226,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -8022,8 +8254,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>21</v>
@@ -8049,8 +8282,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -8071,8 +8305,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -8093,8 +8328,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -8115,8 +8351,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -8137,8 +8374,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -8159,8 +8397,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -8181,8 +8420,9 @@
       <c r="P30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5">
+      <c r="A31" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>28</v>
@@ -8203,8 +8443,9 @@
       <c r="P31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -8225,8 +8466,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -8247,8 +8489,9 @@
       <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -8458,8 +8701,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -8490,8 +8734,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -8522,8 +8767,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -8554,8 +8800,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -8586,8 +8833,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -8618,8 +8866,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -8650,8 +8899,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -8672,8 +8922,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -8694,8 +8945,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -8721,8 +8973,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -8748,8 +9001,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -8775,8 +9029,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -8802,8 +9057,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -8825,8 +9081,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -8852,8 +9109,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -8879,8 +9137,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -8906,8 +9165,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -8929,8 +9189,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -8956,8 +9217,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -8983,8 +9245,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -9010,8 +9273,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -9037,8 +9301,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -9059,8 +9324,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -9081,8 +9347,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -9103,8 +9370,9 @@
       <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5">
+      <c r="A28" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -9125,8 +9393,9 @@
       <c r="P28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -9147,8 +9416,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -9169,8 +9439,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -9191,8 +9462,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -9213,8 +9485,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -9424,8 +9697,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -9456,8 +9730,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>2</v>
@@ -9488,8 +9763,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -9520,8 +9796,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -9552,8 +9829,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -9584,8 +9862,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -9616,8 +9895,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -9638,8 +9918,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>8</v>
@@ -9660,8 +9941,9 @@
       <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>9</v>
@@ -9687,8 +9969,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -9714,8 +9997,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -9741,8 +10025,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -9768,8 +10053,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -9791,8 +10077,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -9818,8 +10105,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>15</v>
@@ -9845,8 +10133,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>16</v>
@@ -9872,8 +10161,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -9895,8 +10185,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -9922,8 +10213,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -9949,8 +10241,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -9976,8 +10269,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -10003,8 +10297,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>22</v>
@@ -10025,8 +10320,9 @@
       <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>23</v>
@@ -10047,8 +10343,9 @@
       <c r="P26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -10069,8 +10366,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -10091,8 +10389,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -10113,8 +10412,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -10135,8 +10435,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -10157,8 +10458,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5">
+      <c r="A32" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>29</v>
@@ -10179,8 +10481,9 @@
       <c r="P32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5">
+      <c r="A33" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>30</v>
@@ -10201,8 +10504,9 @@
       <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9">
+      <c r="A34" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>31</v>
@@ -10412,8 +10716,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -10444,8 +10749,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -10476,8 +10782,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>3</v>
@@ -10508,8 +10815,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9">
+      <c r="A7" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>4</v>
@@ -10540,8 +10848,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>5</v>
@@ -10572,8 +10881,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>6</v>
@@ -10604,8 +10914,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -10626,8 +10937,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -10648,8 +10960,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -10675,8 +10988,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9">
+      <c r="A13" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>10</v>
@@ -10702,8 +11016,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
+      <c r="A14" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>11</v>
@@ -10729,8 +11044,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>12</v>
@@ -10756,8 +11072,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>13</v>
@@ -10779,8 +11096,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -10806,8 +11124,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -10833,8 +11152,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -10860,8 +11180,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>17</v>
@@ -10883,8 +11204,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>18</v>
@@ -10910,8 +11232,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>19</v>
@@ -10937,8 +11260,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>20</v>
@@ -10964,8 +11288,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -10991,8 +11316,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -11013,8 +11339,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -11035,8 +11362,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9">
+      <c r="A27" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>24</v>
@@ -11057,8 +11385,9 @@
       <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9">
+      <c r="A28" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B28" s="9" t="n">
         <v>25</v>
@@ -11079,8 +11408,9 @@
       <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5">
+      <c r="A29" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>26</v>
@@ -11101,8 +11431,9 @@
       <c r="P29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5">
+      <c r="A30" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>27</v>
@@ -11123,8 +11454,9 @@
       <c r="P30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -11145,8 +11477,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -11167,8 +11500,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -11378,8 +11712,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9">
+      <c r="A4" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B4),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
@@ -11410,8 +11745,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B5),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
@@ -11442,8 +11778,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B6),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -11474,8 +11811,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B7),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>4</v>
@@ -11506,8 +11844,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B8),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>5</v>
@@ -11538,8 +11877,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9">
+      <c r="A9" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B9),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>6</v>
@@ -11570,8 +11910,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B10),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>7</v>
@@ -11592,8 +11933,9 @@
       <c r="P10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9">
+      <c r="A11" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B11),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>8</v>
@@ -11614,8 +11956,9 @@
       <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9">
+      <c r="A12" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B12),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>9</v>
@@ -11641,8 +11984,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B13),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>10</v>
@@ -11668,8 +12012,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B14),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>11</v>
@@ -11695,8 +12040,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9">
+      <c r="A15" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B15),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
@@ -11722,8 +12068,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
+      <c r="A16" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B16),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
@@ -11745,8 +12092,9 @@
       <c r="R16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9">
+      <c r="A17" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B17),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>14</v>
@@ -11772,8 +12120,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
+      <c r="A18" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B18),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>15</v>
@@ -11799,8 +12148,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9">
+      <c r="A19" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B19),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>16</v>
@@ -11826,8 +12176,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B20),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>17</v>
@@ -11849,8 +12200,9 @@
       <c r="R20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B21),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>18</v>
@@ -11876,8 +12228,9 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9">
+      <c r="A22" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B22),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>19</v>
@@ -11903,8 +12256,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9">
+      <c r="A23" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B23),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>20</v>
@@ -11930,8 +12284,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
+      <c r="A24" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B24),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>21</v>
@@ -11957,8 +12312,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B25),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>22</v>
@@ -11979,8 +12335,9 @@
       <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9">
+      <c r="A26" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B26),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B26" s="9" t="n">
         <v>23</v>
@@ -12001,8 +12358,9 @@
       <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5">
+      <c r="A27" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B27),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>24</v>
@@ -12023,8 +12381,9 @@
       <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5">
+      <c r="A28" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B28),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>domenica</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>25</v>
@@ -12045,8 +12404,9 @@
       <c r="P28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9">
+      <c r="A29" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B29),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>lunedì</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>26</v>
@@ -12067,8 +12427,9 @@
       <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9">
+      <c r="A30" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B30),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>martedì</v>
       </c>
       <c r="B30" s="9" t="n">
         <v>27</v>
@@ -12089,8 +12450,9 @@
       <c r="P30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9">
+      <c r="A31" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B31),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>mercoledì</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>28</v>
@@ -12111,8 +12473,9 @@
       <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9">
+      <c r="A32" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B32),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>giovedì</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>29</v>
@@ -12133,8 +12496,9 @@
       <c r="P32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9">
+      <c r="A33" s="9" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B33),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>venerdì</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>30</v>
@@ -12155,8 +12519,9 @@
       <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5">
+      <c r="A34" s="5" t="str">
         <f>CHOOSE(WEEKDAY(DATE($B$1,$A$2,B34),2),"lunedì","martedì","mercoledì","giovedì","venerdì","sabato","domenica")</f>
+        <v>sabato</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>31</v>

--- a/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
+++ b/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ottobre 2027" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 

--- a/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
+++ b/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +135,14 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -514,8 +527,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +799,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -819,12 +832,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -852,12 +865,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1108,7 @@
       <c r="P18" s="6" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1136,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1162,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -1173,11 +1190,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -1203,7 +1216,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1244,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -1257,11 +1270,7 @@
       <c r="N24" s="6" t="n"/>
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="str">
@@ -1285,6 +1294,11 @@
       <c r="N25" s="6" t="n"/>
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -1308,6 +1322,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -1331,6 +1350,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -1400,6 +1424,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="str">
@@ -1423,6 +1452,11 @@
       <c r="N31" s="6" t="n"/>
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="str">
@@ -1446,6 +1480,11 @@
       <c r="N32" s="6" t="n"/>
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -1469,7 +1508,174 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
-    </row>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -1477,8 +1683,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1491,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1510,8 +1716,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1782,12 +1988,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -1815,12 +2021,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -1848,12 +2054,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2297,7 @@
       <c r="P18" s="6" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2325,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2351,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -2169,11 +2379,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -2199,7 +2405,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2433,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -2253,11 +2459,7 @@
       <c r="N24" s="6" t="n"/>
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="str">
@@ -2281,6 +2483,11 @@
       <c r="N25" s="6" t="n"/>
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -2304,6 +2511,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -2327,6 +2539,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -2396,6 +2613,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="str">
@@ -2419,6 +2641,11 @@
       <c r="N31" s="6" t="n"/>
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="str">
@@ -2442,6 +2669,11 @@
       <c r="N32" s="6" t="n"/>
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -2465,6 +2697,11 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="str">
@@ -2488,7 +2725,167 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -2496,8 +2893,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2510,7 +2907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2529,8 +2926,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2801,12 +3198,12 @@
       <c r="P7" s="6" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -2834,12 +3231,12 @@
       <c r="P8" s="6" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -2867,12 +3264,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3507,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3535,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3561,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="str">
@@ -3188,11 +3589,7 @@
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="str">
@@ -3218,7 +3615,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3643,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -3272,11 +3669,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -3300,6 +3693,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -3323,6 +3721,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -3346,6 +3749,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="str">
@@ -3415,6 +3823,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -3438,6 +3851,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -3461,6 +3879,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -3484,7 +3907,174 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
-    </row>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -3492,8 +4082,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3506,7 +4096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3525,8 +4115,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3797,12 +4387,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -3830,12 +4420,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -3863,12 +4453,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4696,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4724,7 @@
       <c r="P19" s="6" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4750,11 @@
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -4184,11 +4778,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -4214,7 +4804,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4832,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -4268,11 +4858,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -4296,6 +4882,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="str">
@@ -4319,6 +4910,11 @@
       <c r="N26" s="6" t="n"/>
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="str">
@@ -4342,6 +4938,11 @@
       <c r="N27" s="6" t="n"/>
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -4411,6 +5012,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -4434,6 +5040,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -4457,6 +5068,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="str">
@@ -4480,6 +5096,11 @@
       <c r="N33" s="6" t="n"/>
       <c r="O33" s="6" t="n"/>
       <c r="P33" s="6" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="str">
@@ -4503,7 +5124,167 @@
       <c r="N34" s="6" t="n"/>
       <c r="O34" s="6" t="n"/>
       <c r="P34" s="6" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -4511,8 +5292,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4525,7 +5306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4544,8 +5325,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4816,12 +5597,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -4849,12 +5630,12 @@
       <c r="P8" s="6" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -4882,12 +5663,12 @@
       <c r="P9" s="6" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5906,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5934,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5960,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -5203,11 +5988,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="str">
@@ -5233,7 +6014,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -5261,7 +6042,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -5287,11 +6068,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -5315,6 +6092,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -5338,6 +6120,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -5361,6 +6148,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -5430,6 +6222,11 @@
       <c r="N30" s="6" t="n"/>
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -5453,6 +6250,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -5476,6 +6278,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -5499,6 +6306,11 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="str">
@@ -5522,7 +6334,167 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -5530,8 +6502,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5544,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5563,8 +6535,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5835,12 +6807,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -5868,12 +6840,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -5901,12 +6873,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -6144,7 +7116,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -6172,7 +7144,7 @@
       <c r="P19" s="6" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -6198,7 +7170,11 @@
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -6222,11 +7198,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -6252,7 +7224,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -6280,7 +7252,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -6306,11 +7278,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -6334,6 +7302,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="str">
@@ -6357,6 +7330,11 @@
       <c r="N26" s="6" t="n"/>
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="str">
@@ -6380,6 +7358,11 @@
       <c r="N27" s="6" t="n"/>
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -6449,6 +7432,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -6472,6 +7460,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -6495,6 +7488,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="str">
@@ -6518,6 +7516,11 @@
       <c r="N33" s="6" t="n"/>
       <c r="O33" s="6" t="n"/>
       <c r="P33" s="6" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="str">
@@ -6541,7 +7544,167 @@
       <c r="N34" s="6" t="n"/>
       <c r="O34" s="6" t="n"/>
       <c r="P34" s="6" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -6549,8 +7712,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6563,7 +7726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6582,8 +7745,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6854,12 +8017,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -6887,12 +8050,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -6920,12 +8083,12 @@
       <c r="P9" s="6" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -7163,7 +8326,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -7191,7 +8354,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -7217,7 +8380,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -7241,11 +8408,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -7271,7 +8434,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -7299,7 +8462,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -7325,11 +8488,7 @@
       <c r="N24" s="6" t="n"/>
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -7353,6 +8512,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -7376,6 +8540,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -7399,6 +8568,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -7468,6 +8642,11 @@
       <c r="N30" s="6" t="n"/>
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="str">
@@ -7491,7 +8670,188 @@
       <c r="N31" s="6" t="n"/>
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
-    </row>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -7499,8 +8859,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7513,7 +8873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7532,8 +8892,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7804,12 +9164,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -7837,12 +9197,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -7870,12 +9230,12 @@
       <c r="P9" s="6" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -8113,7 +9473,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -8141,7 +9501,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -8167,7 +9527,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -8191,11 +9555,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -8221,7 +9581,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -8249,7 +9609,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -8275,11 +9635,7 @@
       <c r="N24" s="6" t="n"/>
       <c r="O24" s="6" t="n"/>
       <c r="P24" s="6" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -8303,6 +9659,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -8326,6 +9687,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -8349,6 +9715,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -8418,6 +9789,11 @@
       <c r="N30" s="6" t="n"/>
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="str">
@@ -8441,6 +9817,11 @@
       <c r="N31" s="6" t="n"/>
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="6" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -8464,6 +9845,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -8487,6 +9873,11 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="str">
@@ -8510,7 +9901,167 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -8518,8 +10069,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8532,7 +10083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8551,8 +10102,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8823,12 +10374,12 @@
       <c r="P7" s="6" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -8856,12 +10407,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -8889,12 +10440,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -9132,7 +10683,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -9160,7 +10711,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -9186,7 +10737,11 @@
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="str">
@@ -9210,11 +10765,7 @@
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -9240,7 +10791,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -9268,7 +10819,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -9294,11 +10845,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -9322,6 +10869,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -9345,6 +10897,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="str">
@@ -9368,6 +10925,11 @@
       <c r="N27" s="6" t="n"/>
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="str">
@@ -9437,6 +10999,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -9460,6 +11027,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -9483,6 +11055,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -9506,7 +11083,174 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
-    </row>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -9514,8 +11258,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9528,7 +11272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9547,8 +11291,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9819,12 +11563,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -9852,12 +11596,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -9885,12 +11629,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -10128,7 +11872,7 @@
       <c r="P18" s="6" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -10156,7 +11900,7 @@
       <c r="P19" s="6" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -10182,7 +11926,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -10206,11 +11954,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -10236,7 +11980,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -10264,7 +12008,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -10290,11 +12034,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="str">
@@ -10318,6 +12058,11 @@
       <c r="N25" s="6" t="n"/>
       <c r="O25" s="6" t="n"/>
       <c r="P25" s="6" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="str">
@@ -10341,6 +12086,11 @@
       <c r="N26" s="6" t="n"/>
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="6" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -10364,6 +12114,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -10433,6 +12188,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -10456,6 +12216,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="str">
@@ -10479,6 +12244,11 @@
       <c r="N32" s="6" t="n"/>
       <c r="O32" s="6" t="n"/>
       <c r="P32" s="6" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="str">
@@ -10502,6 +12272,11 @@
       <c r="N33" s="6" t="n"/>
       <c r="O33" s="6" t="n"/>
       <c r="P33" s="6" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="str">
@@ -10525,7 +12300,167 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="10" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -10533,8 +12468,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10547,7 +12482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10566,8 +12501,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10838,12 +12773,12 @@
       <c r="P7" s="10" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -10871,12 +12806,12 @@
       <c r="P8" s="6" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -10904,12 +12839,12 @@
       <c r="P9" s="6" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -11147,7 +13082,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -11175,7 +13110,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -11201,7 +13136,11 @@
       <c r="N20" s="10" t="n"/>
       <c r="O20" s="10" t="n"/>
       <c r="P20" s="10" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="str">
@@ -11225,11 +13164,7 @@
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="str">
@@ -11255,7 +13190,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -11283,7 +13218,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -11309,11 +13244,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -11337,6 +13268,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -11360,6 +13296,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="str">
@@ -11383,6 +13324,11 @@
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="str">
@@ -11452,6 +13398,11 @@
       <c r="N30" s="6" t="n"/>
       <c r="O30" s="6" t="n"/>
       <c r="P30" s="6" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -11475,6 +13426,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -11498,6 +13454,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -11521,7 +13482,174 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
-    </row>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -11529,8 +13657,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11543,7 +13671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11562,8 +13690,8 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="131" customWidth="1" min="19" max="19"/>
+    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11834,12 +13962,12 @@
       <c r="P7" s="6" t="n"/>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Xn</t>
+          <t>Xg</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>non disponibile la notte</t>
+          <t>non disponibile di giorno, cioè mattina e pomeriggio: la notte resta disponibile</t>
         </is>
       </c>
     </row>
@@ -11867,12 +13995,12 @@
       <c r="P8" s="10" t="n"/>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>Gn</t>
+          <t>Xn</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>guardia notte in ALTRA SEDE, blocca tutto il giorno stesso e tutto il giorno successivo. È una notte svolta da un'altra struttura</t>
+          <t>non disponibile la notte</t>
         </is>
       </c>
     </row>
@@ -11900,12 +14028,12 @@
       <c r="P9" s="10" t="n"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>noG</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>congresso, blocca tutto il giorno</t>
+          <t>indisponibile per il turno GUARDIA quel giorno</t>
         </is>
       </c>
     </row>
@@ -12143,7 +14271,7 @@
       <c r="P18" s="10" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 3 sei assente solo la mattina, scrivi Xm sulla riga del giorno 3</t>
+          <t xml:space="preserve">  il giorno 3 sei assente solo la mattina: Xm sulla riga del 3</t>
         </is>
       </c>
     </row>
@@ -12171,7 +14299,7 @@
       <c r="P19" s="10" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  se il giorno 10 sei assente tutto il giorno, scrivi X sulla riga del giorno 10</t>
+          <t xml:space="preserve">  il giorno 10 sei assente tutto il giorno: X sulla riga del 10</t>
         </is>
       </c>
     </row>
@@ -12197,7 +14325,11 @@
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
-      <c r="R20" s="11" t="inlineStr"/>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  il giorno 12 sei assente di giorno ma la notte puoi: Xg sulla riga del 12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="str">
@@ -12221,11 +14353,7 @@
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>ATTENZIONE al codice Gn: blocca anche il giorno successivo.</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="str">
@@ -12251,7 +14379,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Va segnato SOLO sul giorno in cui comincia. Se sei in turno il giorno 4,</t>
+          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -12279,7 +14407,7 @@
       <c r="P23" s="10" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  scrivi Gn sulla riga del 4 e NON scrivere niente sulla riga del 5:</t>
+          <t>una sul giorno in cui comincia e una sul giorno dopo, quando smonti.</t>
         </is>
       </c>
     </row>
@@ -12305,11 +14433,7 @@
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  il blocco del giorno dopo è già compreso nel significato del codice.</t>
-        </is>
-      </c>
+      <c r="R24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="str">
@@ -12333,6 +14457,11 @@
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="R25" s="11" t="inlineStr">
+        <is>
+          <t>I codici noG sono diversi dagli</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="str">
@@ -12356,6 +14485,11 @@
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="10" t="n"/>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>altri: non bloccano una parte della giornata, ma una sola attività in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="str">
@@ -12379,6 +14513,11 @@
       <c r="N27" s="6" t="n"/>
       <c r="O27" s="6" t="n"/>
       <c r="P27" s="6" t="n"/>
+      <c r="R27" s="11" t="inlineStr">
+        <is>
+          <t>quel giorno. Chi li usa resta disponibile per tutto il resto.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="str">
@@ -12448,6 +14587,11 @@
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="10" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE — facoltative</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="str">
@@ -12471,6 +14615,11 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>Spazio libero, facoltativo: si può lasciare vuoto.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="str">
@@ -12494,6 +14643,11 @@
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="10" t="n"/>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Serve a chi prepara l'orario, per le ultime correzioni a mano.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="str">
@@ -12517,6 +14671,11 @@
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
+      <c r="R33" s="12" t="inlineStr">
+        <is>
+          <t>Non viene incollato nel file dei turni e non lo legge nessun programma:</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="str">
@@ -12540,7 +14699,167 @@
       <c r="N34" s="6" t="n"/>
       <c r="O34" s="6" t="n"/>
       <c r="P34" s="6" t="n"/>
-    </row>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>quello che conta per l'assegnazione sono i codici, non queste righe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>Il file gira tra i colleghi, quindi lo leggono tutti: scrivi solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="R36" s="12" t="inlineStr">
+        <is>
+          <t>quello che ti va di far sapere, e non serve dire il motivo di un'assenza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="12" t="inlineStr">
+        <is>
+          <t>Esempi: «il 10 ho messo Xm ma riesco ad arrivare per le 11»,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>«il 14 ho un impegno leggero, se serve posso dare una mano».</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>PERSONA</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>LEONI</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI M</t>
+        </is>
+      </c>
+      <c r="S42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>ROSSI L</t>
+        </is>
+      </c>
+      <c r="S43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>GALLINA</t>
+        </is>
+      </c>
+      <c r="S44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>RUSSO</t>
+        </is>
+      </c>
+      <c r="S45" s="14" t="n"/>
+    </row>
+    <row r="46">
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>VERDI</t>
+        </is>
+      </c>
+      <c r="S46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="S47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>MARINI</t>
+        </is>
+      </c>
+      <c r="S48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>CONTI A</t>
+        </is>
+      </c>
+      <c r="S49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>CONTI S</t>
+        </is>
+      </c>
+      <c r="S50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="R51" s="13" t="inlineStr">
+        <is>
+          <t>FERRARI</t>
+        </is>
+      </c>
+      <c r="S51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="R52" s="13" t="inlineStr">
+        <is>
+          <t>GRECO</t>
+        </is>
+      </c>
+      <c r="S52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="R53" s="13" t="inlineStr">
+        <is>
+          <t>SANNA</t>
+        </is>
+      </c>
+      <c r="S53" s="14" t="n"/>
+    </row>
+    <row r="54">
+      <c r="R54" s="13" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="S54" s="14" t="n"/>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
@@ -12548,8 +14867,8 @@
     <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xn, Gn, C. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
-      <formula1>"X,Xm,Xp,Xn,Gn,C"</formula1>
+    <dataValidation sqref="C4:P34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Codice non ammesso" error="Codice non ammesso: seleziona un valore dall'elenco" promptTitle="Codici ammessi" prompt="Codici ammessi: X, Xm, Xp, Xg, Xn, noG. Il significato di ciascuno è nella legenda, a destra del foglio." type="list">
+      <formula1>"X,Xm,Xp,Xg,Xn,noG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
+++ b/esempi/Indisponibilita_Nov2026_Ott2027.xlsx
@@ -527,7 +527,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -1216,7 +1216,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -2405,7 +2405,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -3615,7 +3615,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -4804,7 +4804,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -6014,7 +6014,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -7224,7 +7224,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -8434,7 +8434,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -9581,7 +9581,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -10791,7 +10791,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -11980,7 +11980,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -13190,7 +13190,7 @@
       <c r="P22" s="6" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="77" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
     <col width="82" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -14379,7 +14379,7 @@
       <c r="P22" s="10" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>Una notte svolta altrove occupa due giornate: si segna con due X,</t>
+          <t>Una notte svolta fuori da questo orario occupa due giornate: si segna con due X,</t>
         </is>
       </c>
     </row>
